--- a/从零开始学Slots/从零开始学Slots-42-基础篇-Grid.xlsx
+++ b/从零开始学Slots/从零开始学Slots-42-基础篇-Grid.xlsx
@@ -6114,6 +6114,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L167" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6799,5 +6802,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M72" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-42-基础篇-Grid.xlsx
+++ b/从零开始学Slots/从零开始学Slots-42-基础篇-Grid.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="189">
   <si>
     <r>
       <rPr>
@@ -5045,7 +5045,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5168,6 +5168,14 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6170,8 +6178,8 @@
       <c r="A5" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>102</v>
+      <c r="B5" s="31">
+        <v>5</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>103</v>
@@ -6419,8 +6427,8 @@
       <c r="E23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>150</v>
+      <c r="A24" s="32">
+        <v>36</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>151</v>
@@ -6432,8 +6440,8 @@
       <c r="E24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>153</v>
+      <c r="A25" s="32">
+        <v>37</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>154</v>
@@ -6445,8 +6453,8 @@
       <c r="E25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>156</v>
+      <c r="A26" s="32">
+        <v>40</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>157</v>
@@ -6458,8 +6466,8 @@
       <c r="E26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>159</v>
+      <c r="A27" s="32">
+        <v>42</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>160</v>
@@ -6471,8 +6479,8 @@
       <c r="E27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>162</v>
+      <c r="A28" s="32">
+        <v>38</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>163</v>
@@ -6484,8 +6492,8 @@
       <c r="E28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>165</v>
+      <c r="A29" s="32">
+        <v>39</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>166</v>

--- a/从零开始学Slots/从零开始学Slots-42-基础篇-Grid.xlsx
+++ b/从零开始学Slots/从零开始学Slots-42-基础篇-Grid.xlsx
@@ -4857,11 +4857,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -5045,7 +5046,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5175,6 +5176,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6686,7 +6699,7 @@
       <c r="A44" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="B44" s="22" t="n">
+      <c r="B44" s="34" t="n">
         <f aca="false">SUM(B40:B43)</f>
         <v>1</v>
       </c>
